--- a/data_tables/qol_skill_text.xlsx
+++ b/data_tables/qol_skill_text.xlsx
@@ -14495,7 +14495,7 @@
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>Left as the game words it (the user, 2026-10-12): the program adds the value where it means to multiply (docs/FORMULAS.md 2.5), so no figure is true of it</t>
+          <t>Left as the game words it (decided 2026-10-12): the program adds the value where it means to multiply (docs/FORMULAS.md 2.5), so no figure is true of it</t>
         </is>
       </c>
     </row>

--- a/data_tables/qol_skill_text.xlsx
+++ b/data_tables/qol_skill_text.xlsx
@@ -580,11 +580,19 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5   |   Speed: 1.5x -&gt; 2x</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -627,11 +635,19 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | Speed: 1.25x -&gt; 1.77x</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -674,16 +690,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -726,16 +749,23 @@
 Accuracy: +20% (+2%/Lv)   |   TP Cost: 5 (+2-3/Lv) -&gt; 28   |   Speed: 0.8x -&gt; 0.9x</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -778,16 +808,23 @@
 Buff cancel rate: 68% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 5 (+1-2/Lv) -&gt; 18   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Buff cancel rate, TP Cost</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -830,11 +867,14 @@
 DEF: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%   |   Turns: 4 -&gt; 8   |   TP Cost: 8 (+2/Lv) -&gt; 16</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -845,6 +885,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -887,11 +930,14 @@
 ATK: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%   |   Turns: 4 -&gt; 8   |   TP Cost: 8 (+2/Lv) -&gt; 16</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -902,6 +948,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -944,11 +993,14 @@
 Stun: 30% -&gt; 32% -&gt; 34% -&gt; 36% -&gt; 38%   |   TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -959,6 +1011,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1001,11 +1056,14 @@
 Accuracy: +5% (+2-3%/Lv) -&gt; +28%   |   Paralysis: 20% -&gt; 50%   |   TP Cost: 6 (+2/Lv) -&gt; 24</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Accuracy, Paralysis</t>
@@ -1016,6 +1074,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1058,16 +1119,23 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1110,11 +1178,14 @@
 Instakill: 10% (+1-2%/Lv) -&gt; 20%   |   Power decrease: 10%   |   TP Cost: 38 (+4/Lv) -&gt; 74</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Instakill</t>
@@ -1125,6 +1196,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1167,11 +1241,19 @@
 Enemy DEF: -16% (-1%/Lv)   |   Turns: 4   |   TP Cost: 14 (+2/Lv) -&gt; 32   |   Speed: 0.8x</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1214,16 +1296,23 @@
 TP Cost: 22 -&gt; 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1266,16 +1355,23 @@
 Critical rate: 10%   |   TP Cost: 36 (+2-3/Lv) -&gt; 61   |   Speed: 0.7x -&gt; 0.8x</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1318,16 +1414,23 @@
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>HP Absorb</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1370,16 +1473,23 @@
 TP Absorb: 10% (+1-2%/Lv) -&gt; 20%   |   TP Cost: 6 (+2/Lv) -&gt; 24   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>TP Absorb</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1422,11 +1532,14 @@
 Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   Accuracy: +14%   |   TP Cost: 9 (+3/Lv) -&gt; 36</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Freeze</t>
@@ -1437,6 +1550,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1479,11 +1595,14 @@
 TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 37 -&gt; 42</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>ATK, Petrify</t>
@@ -1494,6 +1613,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1546,6 +1668,8 @@
           <t>Edited by hand</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -1556,6 +1680,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1598,16 +1725,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 10 -&gt; 14 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1650,16 +1784,23 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1702,11 +1843,14 @@
 Accuracy: +6% -&gt; +20%   |   Damage vs. unholy: +65%   |   TP Cost: 12 (+3/Lv) -&gt; 39</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -1717,6 +1861,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1759,16 +1906,23 @@
 Turns: 5   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1811,16 +1965,23 @@
 Turns: 5   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1863,16 +2024,23 @@
 Paralysis: 20% (+2-3%/Lv) -&gt; 40%   |   TP Cost: 26 (+4-5/Lv) -&gt; 64   |   Speed: 0.8x</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Paralysis, TP Cost</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1915,11 +2083,14 @@
 Silence: 20% (+3-4%/Lv) -&gt; 50%   |   Accuracy: +15%   |   TP Cost: 7 (+3/Lv) -&gt; 34</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Silence</t>
@@ -1930,6 +2101,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1972,16 +2146,23 @@
 Heavy Lance bonus: +20%   |   TP Cost: 36 (+3-6/Lv) -&gt; 71   |   Speed: 0.7x -&gt; 0.8x</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2024,16 +2205,23 @@
 Accuracy: +5% (+1-2%/Lv) -&gt; +15%   |   TP Cost: 32 (+3/Lv) -&gt; 59   |   Speed: 0.8x</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2072,15 +2260,23 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Damage: 1.05x -&gt; 1.1x -&gt; 1.16x -&gt; 1.22x -&gt; 1.3x (L1-5 Max)
+          <t>Damage: 2.05x -&gt; 2.1x -&gt; 2.16x -&gt; 2.22x -&gt; 2.3x (L1-5 Max)
 Turns: 2   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Speed: 0.84x -&gt; 0.9x</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2122,11 +2318,19 @@
 Speed: 1x -&gt; 1.5x</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2168,11 +2372,19 @@
 Speed: 0.6x -&gt; 0.8x</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2215,11 +2427,19 @@
 TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 -&gt; 28 -&gt; 30   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2262,11 +2482,19 @@
 TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 35 -&gt; 38   |   Speed: 0.85x</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2309,16 +2537,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2361,11 +2596,19 @@
 TP Cost: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2408,11 +2651,14 @@
 Turns: 5 -&gt; 9   |   TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -2423,6 +2669,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2475,6 +2724,13 @@
           <t>Edited by hand</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2517,16 +2773,23 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>Physical evasion, Magic evasion</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2569,16 +2832,23 @@
 Sleep: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2621,16 +2891,23 @@
 Silence: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>Silence</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2673,16 +2950,23 @@
 Stun: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>Stun</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2735,11 +3019,17 @@
           <t>Edited by hand</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>ATK, Power decrease, TP Cost</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2782,11 +3072,19 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16   |   Speed: 1x -&gt; 1.12x</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2829,11 +3127,19 @@
 TP Cost: 42 -&gt; 50 -&gt; 57 -&gt; 63 -&gt; 68   |   Speed: 0.4x</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2876,16 +3182,23 @@
 Poison: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>Poison</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2928,16 +3241,23 @@
 Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 8 (+2/Lv) -&gt; 26</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Freeze</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2980,16 +3300,23 @@
 Paralysis: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 8 (+2/Lv) -&gt; 26</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>Paralysis</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3032,16 +3359,23 @@
 Slow: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 9 (+2/Lv) -&gt; 27   |   Speed: 0.95x</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>Slow</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3084,11 +3418,19 @@
 TP Cost: 20 -&gt; 23 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48   |   Speed: 0.65x</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3151,6 +3493,11 @@
           <t>effect_2</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3193,16 +3540,23 @@
 Critical rate: 5% (+1-3%/Lv) -&gt; 25%   |   TP Cost: 24 (+3-4/Lv) -&gt; 55   |   Speed: 0.7x</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>Critical rate, TP Cost</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3245,11 +3599,14 @@
 Turns: 4   |   TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>ATK, Speed decrease chance</t>
@@ -3260,6 +3617,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3302,11 +3662,14 @@
 Stun: 10% -&gt; 20%   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Stun</t>
@@ -3317,6 +3680,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3358,11 +3724,19 @@
 TP Cost: 10 -&gt; 8 -&gt; 6 -&gt; 4 -&gt; 2</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3405,16 +3779,23 @@
 Magic accuracy: -2% (-2%/Lv)   |   Turns: 6   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 32</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3457,11 +3838,14 @@
 Accuracy: +10% (+2-4%/Lv) -&gt; +30%   |   ATK: 82%   |   TP Cost: 28 (+4/Lv) -&gt; 64</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -3472,6 +3856,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3514,16 +3901,23 @@
 Turns: 4   |   TP Cost: 25 -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 48 -&gt; 51 -&gt; 54 -&gt; 57</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3566,16 +3960,23 @@
 TP Cost: 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 57 -&gt; 62 -&gt; 67 -&gt; 73 -&gt; 79</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3618,11 +4019,14 @@
 Turns: 4 -&gt; 7   |   TP Cost: 22 -&gt; 25 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 56</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -3633,6 +4037,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3675,11 +4082,19 @@
 Turns: 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 6   |   TP Cost: 52 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 92   |   Speed: 1.25x</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3722,16 +4137,23 @@
 Accuracy: +10% (+1-2%/Lv) -&gt; +20%   |   TP Cost: 13 (+3-4/Lv) -&gt; 45   |   Speed: 0.9x -&gt; 1x</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3774,16 +4196,23 @@
 Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   Silence: 20% -&gt; 50%   |   TP Cost: 9 (+3/Lv) -&gt; 36</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>Freeze, Silence</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3826,11 +4255,19 @@
 TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 36 -&gt; 40 -&gt; 43 -&gt; 46 -&gt; 49 -&gt; 52 -&gt; 55</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3856,16 +4293,26 @@
           <t>Detect how many unopened treasure chests are left on the current floor.</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>Detect how many unopened treasure chests are left on this floor.</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3906,11 +4353,19 @@
           <t>HP recovery: 12% -&gt; 15% -&gt; 18% -&gt; 21% -&gt; 25% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3952,11 +4407,19 @@
 Speed: 0.85x</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3997,11 +4460,19 @@
           <t>TP transfer bonus: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4043,11 +4514,19 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4089,11 +4568,19 @@
 Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4135,11 +4622,19 @@
 Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4181,11 +4676,19 @@
 Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4227,11 +4730,19 @@
 Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4273,11 +4784,19 @@
 Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4320,16 +4839,23 @@
 Total damage cap: 250 -&gt; 275 -&gt; 300 -&gt; 325 -&gt; 350 -&gt; 375 -&gt; 400 -&gt; 430 -&gt; 460 -&gt; 500</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4371,11 +4897,19 @@
 Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4417,11 +4951,19 @@
 Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4464,16 +5006,23 @@
 Power decrease: 10%   |   TP Cost: 22 (+3-4/Lv) -&gt; 50   |   Speed: 0.75x -&gt; 0.85x</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4516,11 +5065,19 @@
 TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46   |   Speed: 0.75x -&gt; 0.8x</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4563,16 +5120,23 @@
 Paralysis: 20% -&gt; 23% -&gt; 26% -&gt; 29% -&gt; 32%   |   TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4615,16 +5179,23 @@
 Accuracy: +20%   |   TP Cost: 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4667,11 +5238,19 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4697,16 +5276,26 @@
           <t>Spin the magic roulette. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>Spin the magic roulette. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4749,16 +5338,23 @@
 Instakill: 15% (+1-2%/Lv) -&gt; 25%   |   TP Cost: 17 (+2/Lv) -&gt; 35   |   Speed: 0.88x</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
           <t>Instakill</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4801,16 +5397,23 @@
 Stun: 40% (+3-4%/Lv) -&gt; 70%   |   TP Cost: 32 (+2/Lv) -&gt; 50   |   Speed: 0.65x</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>Stun</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4853,16 +5456,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4888,16 +5498,26 @@
           <t>Open a magic box. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>Open a magic box. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4940,11 +5560,19 @@
 TP Cost: 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32   |   Speed: 0.85x</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4987,16 +5615,23 @@
 Poison: 50% (+3-4%/Lv) -&gt; 80%   |   TP Cost: 22 (+4/Lv) -&gt; 58   |   Speed: 0.6x -&gt; 0.7x</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>Poison</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5039,16 +5674,23 @@
 Turn delay rate: 25% (+2%/Lv)   |   TP Cost: 10 (+2-3/Lv) -&gt; 32   |   Speed: 0.95x</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5074,6 +5716,7 @@
           <t>Fan skill. With increased ATK, deal long-range damage to one enemy.</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>Fan skill. With raised ATK, deal minor long-range damage to an enemy.</t>
@@ -5085,11 +5728,19 @@
 Speed: 1.15x</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5132,16 +5783,23 @@
 TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50   |   Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>Slow</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5184,16 +5842,23 @@
 Turns: 6   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 23 -&gt; 25   |   Speed: 0.85x</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>Max HP reduction</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5236,11 +5901,19 @@
 Turns: 2   |   TP Cost: 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50   |   Speed: 1.15x</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5266,16 +5939,26 @@
           <t>Something emerges from the shadows. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>Something emerges from the shadows. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5318,6 +6001,7 @@
 Accuracy UP   |   TP Cost: 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -5328,11 +6012,16 @@
           <t>Accuracy UP</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5395,11 +6084,15 @@
           <t>effect_1</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5462,6 +6155,11 @@
           <t>effect_1</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5524,6 +6222,11 @@
           <t>effect_1</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5586,6 +6289,11 @@
           <t>effect_1</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5628,11 +6336,19 @@
 Duration: 5   |   TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38   |   Speed: 1.15x</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5695,6 +6411,11 @@
           <t>effect_1</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5737,11 +6458,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5784,11 +6513,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5831,11 +6568,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5878,11 +6623,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5925,11 +6678,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5972,11 +6733,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6019,11 +6788,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6066,11 +6843,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6113,11 +6898,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6160,11 +6953,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6207,11 +7008,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6254,11 +7063,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6301,11 +7118,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6348,11 +7173,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6395,11 +7228,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6442,11 +7283,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6489,11 +7338,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6536,11 +7393,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6583,11 +7448,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6630,11 +7503,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6677,11 +7558,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6724,11 +7613,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6771,11 +7668,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6818,11 +7723,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6865,11 +7778,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6912,11 +7833,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6959,11 +7888,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7006,11 +7943,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7053,11 +7998,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7100,11 +8053,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7147,11 +8108,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7194,11 +8163,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7241,11 +8218,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7288,11 +8273,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7335,11 +8328,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7382,11 +8383,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7429,11 +8438,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7476,11 +8493,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7523,11 +8548,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7570,11 +8603,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7617,11 +8658,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7664,11 +8713,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7711,11 +8768,14 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -7726,6 +8786,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7768,11 +8831,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -7783,6 +8849,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7825,11 +8894,14 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -7840,6 +8912,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7882,11 +8957,19 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7929,11 +9012,14 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -7944,6 +9030,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7986,11 +9075,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8001,6 +9093,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8043,11 +9138,14 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8058,6 +9156,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8100,11 +9201,19 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8147,11 +9256,14 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -8162,6 +9274,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8204,11 +9319,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8219,6 +9337,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8261,11 +9382,14 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8276,6 +9400,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8318,11 +9445,19 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8365,11 +9500,14 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -8380,6 +9518,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8422,11 +9563,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8437,6 +9581,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8479,11 +9626,14 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8494,6 +9644,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8536,11 +9689,19 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8583,11 +9744,14 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -8598,6 +9762,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8640,11 +9807,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8655,6 +9825,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8697,11 +9870,14 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8712,6 +9888,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8754,11 +9933,19 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8801,11 +9988,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   HP Absorb: 100%   |   TP Cost: 9 (+1/Lv) -&gt; 18</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -8816,6 +10006,9 @@
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8858,16 +10051,23 @@
 TP Absorb: 100% | TP Cost: 6 (+1/Lv) -&gt; 15 | Speed: 1.75x | Chant: 1.25x -&gt; 1.07x</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8910,16 +10110,23 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 27 -&gt; 31 -&gt; 35 -&gt; 39 -&gt; 43   |   Speed: 1.5x</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8962,11 +10169,14 @@
 TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50   |   Speed: 1.5x</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
           <t>Pwr, Accuracy</t>
@@ -8977,6 +10187,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9019,11 +10232,19 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18   |   Speed: 0.8x -&gt; 0.92x   |   Chant: 1.25x</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9066,11 +10287,19 @@
 TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   Speed: 2.15x   |   Chant: 1.2x -&gt; 1.4x</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9113,11 +10342,19 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9160,11 +10397,19 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1x -&gt; 1.2x</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9207,11 +10452,19 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9254,11 +10507,19 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9301,11 +10562,19 @@
 TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9348,11 +10617,19 @@
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9395,11 +10672,19 @@
 TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23   |   Chant: 1x -&gt; 1.12x</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9442,11 +10727,19 @@
 TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30   |   Speed: 0.4x -&gt; 0.5x   |   Chant: 1.25x</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9489,11 +10782,19 @@
 TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 18 -&gt; 22   |   Speed: 1.25x   |   Chant: 1.25x -&gt; 1.45x</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9536,11 +10837,14 @@
 TP Cost: 45 -&gt; 52 -&gt; 59 -&gt; 66 -&gt; 74 -&gt; 80 -&gt; 86 -&gt; 90 -&gt; 95 -&gt; 100   |   Speed: 1.75x</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
           <t>Pwr, Accuracy</t>
@@ -9551,6 +10855,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9593,11 +10900,19 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9640,11 +10955,19 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9687,11 +11010,19 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9734,11 +11065,19 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9781,11 +11120,19 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9828,16 +11175,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9880,16 +11234,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9932,16 +11293,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9984,11 +11352,14 @@
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26   |   Speed: 1.75x</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
           <t>Heal Cap</t>
@@ -9999,6 +11370,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10041,11 +11415,14 @@
 TP Cost: 15 -&gt; 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46 -&gt; 52 -&gt; 58 -&gt; 64   |   Speed: 1.35x</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr">
         <is>
           <t>Heal Cap</t>
@@ -10056,6 +11433,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10096,11 +11476,19 @@
           <t>TP Cost: 48 -&gt; 45 -&gt; 42 -&gt; 39 -&gt; 36 (L1-5 Max)   |   Speed: 1.15x   |   Chant: 1.5x -&gt; 1.75x</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10143,11 +11531,19 @@
 TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   Speed: 2.25x   |   Chant: 2.75x</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10190,11 +11586,19 @@
 TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 36   |   Speed: 1.5x   |   Chant: 2x</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10237,11 +11641,19 @@
 TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42   |   Speed: 1.25x   |   Chant: 1.3x -&gt; 1.5x</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10284,16 +11696,23 @@
 Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17   |   Chant: 1.25x</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10336,16 +11755,23 @@
 Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17   |   Chant: 1.25x</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10388,16 +11814,23 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32   |   Chant: 1.25x</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10440,16 +11873,23 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32   |   Chant: 1.25x</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10492,16 +11932,23 @@
 Turns: 3   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Speed: 1.25x -&gt; 1.41x</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10544,16 +11991,23 @@
 Turns: 5 -&gt; 5 -&gt; 6 -&gt; 6 -&gt; 7 -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 18 (+3/Lv) -&gt; 45</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10596,11 +12050,19 @@
 TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 21 -&gt; 24 -&gt; 28   |   Speed: 1.75x   |   Chant: 2.25x</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10643,11 +12105,19 @@
 Chant: 0.75x -&gt; 0.65x</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10690,11 +12160,19 @@
 Turns: 4   |   TP Cost: 24 -&gt; 28 -&gt; 33 -&gt; 37 -&gt; 42   |   Speed: 1.5x   |   Chant: 0.75x</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10737,16 +12215,23 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 45   |   Speed: 1.5x</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10787,11 +12272,19 @@
           <t>Turns: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10832,11 +12325,19 @@
           <t>TP Cost: 28 -&gt; 21 -&gt; 14 -&gt; 7 -&gt; 1 (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10878,11 +12379,19 @@
 Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10908,6 +12417,7 @@
           <t>Raise the party's chance of doing multiple strikes while song lasts.</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>Raise the party's chance of doing multiple strikes while song lasts.</t>
@@ -10918,11 +12428,19 @@
           <t>Speed: 1.35x   |   Chant: 1.4x</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10964,11 +12482,19 @@
 Speed: 1.35x   |   Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11010,11 +12536,19 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11056,11 +12590,19 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11102,11 +12644,19 @@
 Speed: 1.35x   |   Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11148,11 +12698,19 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11194,11 +12752,19 @@
 Speed: 1.35x   |   Chant: 1.1x -&gt; 1.5x</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11240,11 +12806,19 @@
 Speed: 1.35x   |   Chant: 1.1x -&gt; 1.5x</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11286,11 +12860,19 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11332,11 +12914,19 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11379,16 +12969,23 @@
 Turns: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5   |   TP Cost: 23 -&gt; 27 -&gt; 32 -&gt; 38 -&gt; 45   |   Speed: 0.85x</t>
         </is>
       </c>
+      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11431,11 +13028,19 @@
 Turns: 3 | TP Cost: 36 -&gt; 39 -&gt; 43 -&gt; 47 -&gt; 52 | Speed: 0.8x | Chant: 0.8x -&gt; 0.88x</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11478,11 +13083,19 @@
 Turns: 3   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Chant: 1.15x -&gt; 1.3x</t>
         </is>
       </c>
+      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11535,6 +13148,8 @@
           <t>Edited by hand</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -11545,6 +13160,9 @@
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11587,11 +13205,14 @@
 Magic defense: -7% -&gt; -18%   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
           <t>Magic defense, Damage cap</t>
@@ -11602,6 +13223,9 @@
           <t>Turns, Speed, Chant</t>
         </is>
       </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11644,11 +13268,14 @@
 Speed decrease: 4% (+1%/Lv)   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -11659,6 +13286,9 @@
           <t>Turns, Speed, Chant</t>
         </is>
       </c>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11711,6 +13341,8 @@
           <t>Edited by hand</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -11721,6 +13353,9 @@
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11773,6 +13408,8 @@
           <t>Edited by hand</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -11783,6 +13420,9 @@
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11825,11 +13465,14 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 22 (+4-6/Lv) -&gt; 66   |   Speed: 1.3x</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -11840,6 +13483,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11882,16 +13528,23 @@
 TP Cost: 36 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 80 -&gt; 88 -&gt; 96   |   Speed: 1.5x</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11934,16 +13587,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22   |   Chant: 1.15x</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11986,16 +13646,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22   |   Chant: 1.15x</t>
         </is>
       </c>
+      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -12038,11 +13705,19 @@
 Turns: 3   |   TP Cost: 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40   |   Speed: 0.75x   |   Chant: 1.75x</t>
         </is>
       </c>
+      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12085,11 +13760,19 @@
 TP Cost: 12 -&gt; 11 -&gt; 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3</t>
         </is>
       </c>
+      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12132,11 +13815,14 @@
 Recoverable status ailments: 1 (+1/Lv)   |   HP on revival: 10% (+5-10%/Lv) -&gt; 50%</t>
         </is>
       </c>
+      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
           <t>HP on revival</t>
@@ -12147,6 +13833,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12199,6 +13888,8 @@
           <t>Edited by hand</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
           <t>Magic defense, Accuracy, HP recovery, TP Cost</t>
@@ -12209,6 +13900,9 @@
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12251,11 +13945,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 30 (+4/Lv) -&gt; 66   |   Speed: 0.85x</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -12266,6 +13963,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12308,11 +14008,14 @@
 TP Cost: 32 -&gt; 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 52 -&gt; 54 -&gt; 56   |   Speed: 1.2x</t>
         </is>
       </c>
+      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
           <t>Pwr</t>
@@ -12323,6 +14026,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12365,6 +14071,7 @@
 TP Cost: 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 (L1-5 Max)   |   Speed: 1.5x   |   Chant: 0.84x -&gt; 0.8x</t>
         </is>
       </c>
+      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -12380,6 +14087,11 @@
           <t>effect_1</t>
         </is>
       </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12422,11 +14134,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12469,11 +14189,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12516,11 +14244,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12563,11 +14299,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -12610,11 +14354,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -12657,11 +14409,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -12702,11 +14462,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -12747,11 +14515,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12792,11 +14568,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17% (L10)</t>
         </is>
       </c>
+      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12837,11 +14621,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12882,11 +14674,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -12927,11 +14727,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr"/>
+      <c r="Q248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12972,11 +14780,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13017,11 +14833,19 @@
           <t>ATK bonus: 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% (L10)</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr"/>
+      <c r="Q250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13062,11 +14886,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17% (L10)</t>
         </is>
       </c>
+      <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13107,11 +14939,19 @@
           <t>ATK bonus: 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% (L10)</t>
         </is>
       </c>
+      <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13152,11 +14992,19 @@
           <t>ATK bonus: 2% -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 12% (L10)</t>
         </is>
       </c>
+      <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13197,11 +15045,19 @@
           <t>Magic attack bonus: 6% -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13243,11 +15099,19 @@
 Heal Cap: +10% -&gt; +20 -&gt; +30 -&gt; +40 -&gt; +50 -&gt; +60 -&gt; +70 -&gt; +80 -&gt; +90 -&gt; +100%</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13288,11 +15152,19 @@
           <t>HP recovery: 2% -&gt; 4% -&gt; 6% -&gt; 8% -&gt; 10% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13333,11 +15205,19 @@
           <t>HP recovery: 1% -&gt; 2% -&gt; 3% -&gt; 4% -&gt; 5% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13378,11 +15258,19 @@
           <t>TP recovery: 3 -&gt; 6 -&gt; 9 -&gt; 12 -&gt; 16 (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13423,11 +15311,19 @@
           <t>TP recovery: 1 -&gt; 3 -&gt; 5 -&gt; 7 -&gt; 9 (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13468,11 +15364,19 @@
           <t>Elemental resistance: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 (L10)</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
+      <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -13513,11 +15417,19 @@
           <t>Counterattack rate: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -13558,11 +15470,19 @@
           <t>Activation rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -13603,11 +15523,19 @@
           <t>Double attack rate: 9% -&gt; 12% -&gt; 15% -&gt; 18% -&gt; 21% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -13648,11 +15576,19 @@
           <t>Triple attack rate: 5% -&gt; 8% -&gt; 11% -&gt; 14% -&gt; 17% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -13693,11 +15629,19 @@
           <t>Evasion rate: 20% -&gt; 24% -&gt; 28% -&gt; 32% -&gt; 36% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr"/>
+      <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -13738,11 +15682,19 @@
           <t>Activation rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -13783,11 +15735,19 @@
           <t>Survival rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr"/>
+      <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -13828,11 +15788,19 @@
           <t>Auto-guard rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -13873,11 +15841,19 @@
           <t>Sub-weapon ATK: 30% -&gt; 35 -&gt; 40 -&gt; 45 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 68 -&gt; 72% (L10)</t>
         </is>
       </c>
+      <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr"/>
+      <c r="P269" t="inlineStr"/>
+      <c r="Q269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -13918,11 +15894,19 @@
           <t>TP conversion: 4% -&gt; 8% -&gt; 12% -&gt; 16% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
+      <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -13963,11 +15947,19 @@
           <t>Activation rate: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr"/>
+      <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14008,11 +16000,19 @@
           <t>Activation rate: 2% -&gt; 3% -&gt; 4% -&gt; 5% -&gt; 6% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr"/>
+      <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14053,11 +16053,19 @@
           <t>Activation rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr"/>
+      <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14098,11 +16106,19 @@
           <t>Speed increase: 15% -&gt; 16% -&gt; 17% -&gt; 18% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr"/>
+      <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14143,11 +16159,19 @@
           <t>Number of possible debuffs: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 (L6)</t>
         </is>
       </c>
+      <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr"/>
+      <c r="P275" t="inlineStr"/>
+      <c r="Q275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14188,11 +16212,19 @@
           <t>ATK: +15% -&gt; +18% -&gt; +21% -&gt; +24% -&gt; +27% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr"/>
+      <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14218,16 +16250,26 @@
           <t>Nullify the effects of enemy Dark Auras.</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
           <t>Nullify the effects of enemy Dark Auras.</t>
         </is>
       </c>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
+      <c r="P277" t="inlineStr"/>
+      <c r="Q277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14253,16 +16295,26 @@
           <t>No longer suffer counterattacks from enemies.</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
           <t>No longer suffer counterattacks from enemies.</t>
         </is>
       </c>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr"/>
+      <c r="P278" t="inlineStr"/>
+      <c r="Q278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14303,11 +16355,19 @@
           <t>Physical damage: -6% -&gt; -7% -&gt; -8% -&gt; -9% -&gt; -10% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
+      <c r="P279" t="inlineStr"/>
+      <c r="Q279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14348,11 +16408,19 @@
           <t>Activation rate: 8% -&gt; 9% -&gt; 10% -&gt; 11% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr"/>
+      <c r="P280" t="inlineStr"/>
+      <c r="Q280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14393,11 +16461,19 @@
           <t>LvUp: Can cure poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; slow</t>
         </is>
       </c>
+      <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr"/>
+      <c r="P281" t="inlineStr"/>
+      <c r="Q281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14438,11 +16514,19 @@
           <t>ATK/DEX: +10% -&gt; +11% -&gt; +12% -&gt; +13% -&gt; +15% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
+      <c r="P282" t="inlineStr"/>
+      <c r="Q282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -14490,14 +16574,16 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="Q283" t="inlineStr">
-        <is>
-          <t>Left as the game words it (decided 2026-10-12): the program adds the value where it means to multiply (docs/FORMULAS.md 2.5), so no figure is true of it</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="inlineStr"/>
+      <c r="Q283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14538,11 +16624,19 @@
           <t>Chant time: -8% -&gt; -11% -&gt; -14% -&gt; -17% -&gt; -20% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14583,11 +16677,19 @@
           <t>TP Cost reduction: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="inlineStr"/>
+      <c r="Q285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14628,11 +16730,19 @@
           <t>Accuracy: 3% -&gt; 5% -&gt; 7% -&gt; 9% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14673,11 +16783,19 @@
           <t>Enemy preemptive attack rate: -20% -&gt; -28% -&gt; -36% -&gt; -44% -&gt; -50% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr"/>
+      <c r="P287" t="inlineStr"/>
+      <c r="Q287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14718,11 +16836,19 @@
           <t>Preemptive attack rate: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="inlineStr"/>
+      <c r="Q288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14763,11 +16889,19 @@
           <t>Battle escape rate: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
+      <c r="Q289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -14808,11 +16942,19 @@
           <t>Item drop rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="inlineStr"/>
+      <c r="Q290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -14853,11 +16995,19 @@
           <t>Gold drop rate: 25% -&gt; 50% -&gt; 75% -&gt; 100% -&gt; 125% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="inlineStr"/>
+      <c r="Q291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -14898,11 +17048,19 @@
           <t>Found item quality: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr"/>
+      <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -14944,11 +17102,19 @@
 Post-battle TP: 3% -&gt; 4% -&gt; 5% -&gt; 7% -&gt; 9%</t>
         </is>
       </c>
+      <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -14989,11 +17155,19 @@
           <t>Item keep rate: 25% -&gt; 27% -&gt; 29% -&gt; 32% -&gt; 35% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="inlineStr"/>
+      <c r="Q294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15034,11 +17208,19 @@
           <t>Item effects: 10% -&gt; 20 -&gt; 30 -&gt; 40 -&gt; 50 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 90 -&gt; 100% (L10)</t>
         </is>
       </c>
+      <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="inlineStr"/>
+      <c r="Q295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15079,11 +17261,19 @@
           <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15124,11 +17314,19 @@
           <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="inlineStr"/>
+      <c r="Q297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15169,11 +17367,19 @@
           <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="inlineStr"/>
+      <c r="Q298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -15214,11 +17420,19 @@
           <t>Sealbook ability: +15% -&gt; +18% -&gt; +21% -&gt; +24% -&gt; +27% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="inlineStr"/>
+      <c r="Q299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -15259,11 +17473,19 @@
           <t>Maid skill bonus: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10% (L10)</t>
         </is>
       </c>
+      <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr"/>
+      <c r="P300" t="inlineStr"/>
+      <c r="Q300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -15304,11 +17526,19 @@
           <t>Singing skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
+      <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="inlineStr"/>
+      <c r="Q301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -15349,11 +17579,19 @@
           <t>Dancing skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
+      <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="inlineStr"/>
+      <c r="Q302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -15394,11 +17632,19 @@
           <t>Doll skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
+      <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="inlineStr"/>
+      <c r="Q303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -15439,11 +17685,19 @@
           <t>Double attack rate: 20% -&gt; 21 -&gt; 22 -&gt; 23 -&gt; 24 -&gt; 25 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32% (L10)</t>
         </is>
       </c>
+      <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr"/>
+      <c r="P304" t="inlineStr"/>
+      <c r="Q304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -15484,11 +17738,19 @@
           <t>Song chant time: -10% -&gt; -11 -&gt; -12 -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -20%</t>
         </is>
       </c>
+      <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="inlineStr"/>
+      <c r="Q305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -15529,11 +17791,19 @@
           <t>Negotiation rate: 10% -&gt; 14% -&gt; 18% -&gt; 22% -&gt; 25% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="inlineStr"/>
+      <c r="Q306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -15574,11 +17844,19 @@
           <t>Occurrence rate: 3% -&gt; 4% -&gt; 5% -&gt; 6% -&gt; 7% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="inlineStr"/>
+      <c r="Q307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -15604,16 +17882,26 @@
           <t>Nullify first hit of battle against user (does not work for status ailments).</t>
         </is>
       </c>
+      <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
           <t>Nullify first hit of battle against user (does not work for status ailments).</t>
         </is>
       </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -15639,16 +17927,26 @@
           <t>Heighten the probability of beneficial results for random effect skills.</t>
         </is>
       </c>
+      <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
           <t>Heighten the probability of beneficial results for random effect skills.</t>
         </is>
       </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="inlineStr"/>
+      <c r="Q309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -15674,16 +17972,26 @@
           <t>Whip skill. Strike back with a normal attack before a targeted attack hits you.</t>
         </is>
       </c>
+      <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
           <t>Whip skill. Strike back with a normal attack before a targeted attack hits you.</t>
         </is>
       </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr"/>
+      <c r="Q310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -15709,16 +18017,26 @@
           <t>Occasionally get the first action regardless of speed.</t>
         </is>
       </c>
+      <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr">
         <is>
           <t>Occasionally get the first action regardless of speed.</t>
         </is>
       </c>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr"/>
+      <c r="Q311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -15744,16 +18062,26 @@
           <t>Occasionally land critical hits with offensive spells.</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
           <t>Occasionally land critical hits with offensive spells.</t>
         </is>
       </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="inlineStr"/>
+      <c r="Q312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -15779,16 +18107,26 @@
           <t>Increase doll summon duration by 1 turn.</t>
         </is>
       </c>
+      <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr">
         <is>
           <t>Increase doll summon duration by 1 turn.</t>
         </is>
       </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr"/>
+      <c r="O313" t="inlineStr"/>
+      <c r="P313" t="inlineStr"/>
+      <c r="Q313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -15814,17 +18152,27 @@
           <t>Significantly increase damage according to Pep.</t>
         </is>
       </c>
+      <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr">
         <is>
           <t>Significantly increase damage according to Pep.
 Pep over 100 per +1% damage: 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3 -&gt; 2   |   Crown EX: 1</t>
         </is>
       </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr"/>
+      <c r="O314" t="inlineStr"/>
+      <c r="P314" t="inlineStr"/>
+      <c r="Q314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -15850,17 +18198,27 @@
           <t>Occasionally inflict enemies with status ailments or Dispel at random.</t>
         </is>
       </c>
+      <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr">
         <is>
           <t>Occasionally inflict enemies with status ailments or Dispel at random.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 25%</t>
         </is>
       </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr"/>
+      <c r="O315" t="inlineStr"/>
+      <c r="P315" t="inlineStr"/>
+      <c r="Q315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -15886,17 +18244,27 @@
           <t>May counter short-range attacks with Slow and a Speed decrease.</t>
         </is>
       </c>
+      <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
           <t>May counter short-range attacks with Slow and a Speed decrease.
 Activation rate: 16% -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38%   |   Crown EX: 50%</t>
         </is>
       </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr"/>
+      <c r="P316" t="inlineStr"/>
+      <c r="Q316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -15922,17 +18290,27 @@
           <t>Increase weapon modifier when attacking with weapon-based skills.</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr">
         <is>
           <t>Increase weapon modifier when attacking with weapon-based skills.
 Weapon modifier: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18%   |   Crown EX: 25%</t>
         </is>
       </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="inlineStr"/>
+      <c r="Q317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -15958,17 +18336,27 @@
           <t>May guarantee a hit and bypass DEF with physical attacks or skills.</t>
         </is>
       </c>
+      <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
           <t>May guarantee a hit and bypass DEF with physical attacks or skills.
 Activation rate: 12% -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20%   |   Crown EX: 30%</t>
         </is>
       </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="inlineStr"/>
+      <c r="Q318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -15994,17 +18382,27 @@
           <t>Occasionally nullify all damage received from enemies.</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr">
         <is>
           <t>Occasionally nullify all damage received from enemies.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr"/>
+      <c r="P319" t="inlineStr"/>
+      <c r="Q319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -16030,17 +18428,27 @@
           <t>Before acting, may erase enemy puppets, familiars, shikigami, or slaves.</t>
         </is>
       </c>
+      <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr">
         <is>
           <t>Before acting, may erase enemy puppets, familiars, shikigami, or slaves.
 Activation rate: 25% -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 49 -&gt; 53 -&gt; 57%   |   Crown EX: 75%</t>
         </is>
       </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="inlineStr"/>
+      <c r="Q320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -16066,17 +18474,27 @@
           <t>Before acting, may use an item from her own personal stock.</t>
         </is>
       </c>
+      <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr">
         <is>
           <t>Before acting, may use an item from her own personal stock.
 Activation rate: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18%   |   Crown EX: 25%</t>
         </is>
       </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr"/>
+      <c r="P321" t="inlineStr"/>
+      <c r="Q321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -16102,17 +18520,27 @@
           <t>Decrease turn delay after using skills or magic.</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr">
         <is>
           <t>Decrease turn delay after using skills or magic.
 Speed added: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr"/>
+      <c r="P322" t="inlineStr"/>
+      <c r="Q322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -16138,17 +18566,27 @@
           <t>Increased effects for all maid skills.</t>
         </is>
       </c>
+      <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr">
         <is>
           <t>Increased effects for all maid skills.
 Maid skill effects: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 10%   |   Crown EX: 13%</t>
         </is>
       </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="inlineStr"/>
+      <c r="Q323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -16174,17 +18612,27 @@
           <t>May occasionally act twice in one turn.</t>
         </is>
       </c>
+      <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
           <t>May occasionally act twice in one turn.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="inlineStr"/>
+      <c r="Q324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -16210,17 +18658,27 @@
           <t>If killed, revive after a certain number of turns.</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr">
         <is>
           <t>If killed, revive after a certain number of turns.
 Activation rate: 8% -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24%   |   Crown EX: 30%</t>
         </is>
       </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr"/>
+      <c r="P325" t="inlineStr"/>
+      <c r="Q325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -16246,17 +18704,27 @@
           <t>Whole row takes less damage from Demons, Undead, and Apparitions.</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
           <t>Whole row takes less damage from Demons, Undead, and Apparitions.
 Taken: -12% -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -19 -&gt; -20%   |   Crown EX: -25%</t>
         </is>
       </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr"/>
+      <c r="P326" t="inlineStr"/>
+      <c r="Q326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -16282,6 +18750,7 @@
           <t>May lower all enemies' ATK and INT with heart-penetrating vocals.</t>
         </is>
       </c>
+      <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr">
         <is>
           <t>May lower all enemies' ATK and INT with heart-penetrating vocals.
@@ -16289,11 +18758,20 @@
 Enemy ATK and INT: -10% for 4 turns</t>
         </is>
       </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr"/>
+      <c r="P327" t="inlineStr"/>
+      <c r="Q327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -16319,17 +18797,27 @@
           <t>Magic will occasionally activate immediately without the need to chant.</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
           <t>Magic will occasionally activate immediately without the need to chant.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
       <c r="J328" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr"/>
+      <c r="P328" t="inlineStr"/>
+      <c r="Q328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -16355,6 +18843,7 @@
           <t>Occasionally reflects a percentage of damage taken as fixed damage.</t>
         </is>
       </c>
+      <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
           <t>Occasionally reflects a percentage of damage taken as fixed damage.
@@ -16362,11 +18851,20 @@
 Activation rate: 15%</t>
         </is>
       </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr"/>
+      <c r="P329" t="inlineStr"/>
+      <c r="Q329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -16392,17 +18890,27 @@
           <t>Summons another self from the shadows to attack.</t>
         </is>
       </c>
+      <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
           <t>Summons another self from the shadows to attack.
 Activation rate: 4% -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12%   |   Crown EX: 20%</t>
         </is>
       </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr"/>
+      <c r="P330" t="inlineStr"/>
+      <c r="Q330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -16428,17 +18936,27 @@
           <t>Increased effects for all class modifiers.</t>
         </is>
       </c>
+      <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr">
         <is>
           <t>Increased effects for all class modifiers.
 Class modifiers (%): 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Crown EX: 15</t>
         </is>
       </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr"/>
+      <c r="P331" t="inlineStr"/>
+      <c r="Q331" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16507,13 +19025,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -16529,13 +19047,13 @@
         <v>87</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
         <v>18</v>
       </c>
       <c r="F3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4">
